--- a/data/trending_integrated_20260918_13.xlsx
+++ b/data/trending_integrated_20260918_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26150</v>
+        <v>26225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.06%</t>
+          <t>'+21.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>299902706900</v>
+        <v>305627923650</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -619,23 +619,23 @@
         <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>-170000</v>
+        <v>-149000</v>
       </c>
       <c r="S2" t="n">
-        <v>44000</v>
+        <v>136000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매물 소화 후 주가 상승 기대감 및 프로그램 매수세 언급. 대장주로서의 흐름 긍정적 전망.</t>
+          <t>외인 폭풍 매수 및 프로그램 매수세 유입으로 강한 상승세. 통신주 대비 저평가 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매물 소화', '프로그램 매수', '대장주']</t>
+          <t>['외인 매수', '프로그램 매수', '상승세']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8170</v>
+        <v>8130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.38%</t>
+          <t>'+15.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G3" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>145597969075</v>
+        <v>147933866255</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -711,7 +711,7 @@
         <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>619000</v>
+        <v>603000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18720</v>
+        <v>18540</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.06%</t>
+          <t>'+14.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G4" t="n">
-        <v>2239</v>
+        <v>2268</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>722783372645</v>
+        <v>746559047610</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -803,10 +803,10 @@
         <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>1514000</v>
+        <v>1339000</v>
       </c>
       <c r="S4" t="n">
-        <v>86000</v>
+        <v>131000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11330</v>
+        <v>31150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.54%</t>
+          <t>'+10.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.29</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="H5" t="n">
-        <v>18.13</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10250</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>10280</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>11500</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>10230</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>18.42</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>157980505685</v>
+        <v>187164534850</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>23000</v>
+        <v>254000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인 매매 동향과 일부 기술적 지표 언급. 주가 상승 및 하락에 대한 상반된 전망 제시.</t>
+          <t>가온전선과의 비교 속 저평가 해소 기대감 형성. 프로그램 매수세와 함께 추세 전환 가능성 탐색.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인', '기술적 지표', '주가 전망']</t>
+          <t>['저평가', '가온전선', '프로그램매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30950</v>
+        <v>12650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.36%</t>
+          <t>'+9.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>191</v>
+        <v>620</v>
       </c>
       <c r="H6" t="n">
-        <v>11.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28300</v>
+        <v>11580</v>
       </c>
       <c r="K6" t="n">
-        <v>28850</v>
+        <v>12200</v>
       </c>
       <c r="L6" t="n">
-        <v>32050</v>
+        <v>13820</v>
       </c>
       <c r="M6" t="n">
-        <v>28550</v>
+        <v>12100</v>
       </c>
       <c r="N6" t="n">
-        <v>11.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>184649616350</v>
+        <v>120678121875</v>
       </c>
       <c r="P6" t="n">
-        <v>75900</v>
+        <v>21150</v>
       </c>
       <c r="Q6" t="n">
-        <v>15000</v>
+        <v>8140</v>
       </c>
       <c r="R6" t="n">
-        <v>253000</v>
+        <v>349000</v>
       </c>
       <c r="S6" t="n">
-        <v>29000</v>
+        <v>156000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 기대감 형성. 프로그램 매수세와 함께 추세 전환 가능성 탐색.</t>
+          <t>셀그램 뉴스 기대감 있으나, 외인/기관 동시 매수세 약화 및 매도세 출현으로 하락 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '가온전선', '프로그램매수']</t>
+          <t>['셀그램', '외인/기관 매매', '하락 우려']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12650</v>
+        <v>6390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.24%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>610</v>
+        <v>184</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11580</v>
+        <v>5880</v>
       </c>
       <c r="K7" t="n">
-        <v>12200</v>
+        <v>5950</v>
       </c>
       <c r="L7" t="n">
-        <v>13820</v>
+        <v>6920</v>
       </c>
       <c r="M7" t="n">
-        <v>12100</v>
+        <v>5840</v>
       </c>
       <c r="N7" t="n">
-        <v>8.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>119585207845</v>
+        <v>87809732305</v>
       </c>
       <c r="P7" t="n">
-        <v>21150</v>
+        <v>11760</v>
       </c>
       <c r="Q7" t="n">
-        <v>8140</v>
+        <v>1620</v>
       </c>
       <c r="R7" t="n">
-        <v>483000</v>
+        <v>733000</v>
       </c>
       <c r="S7" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>호재성 뉴스 언급에도 불구하고 주가 하락 및 손실에 대한 부정적 경험 공유. 매도 권유.</t>
+          <t>박스권 돌파 및 전력/변압기 관련 사업 성장 기대감. 전환사채 발행 예정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 하락', '손실', '매도']</t>
+          <t>['박스권 돌파', '전력', '변압기']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6370</v>
+        <v>13930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+8.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5880</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>5950</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>6920</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>5840</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>87016729155</v>
+        <v>139166667265</v>
       </c>
       <c r="P8" t="n">
-        <v>11760</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>1620</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>691000</v>
+        <v>110000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>전환사채 발행 이후 박스권 돌파 및 전력/변압기 관련주 주목. 외국인/프로그램 매수세 유입으로 인한 주가 상승 기대.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전환사채', '박스권돌파', '외국인매수']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,104 +1195,104 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13840</v>
+        <v>11100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.62%</t>
+          <t>'+8.29%</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10250</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10230</v>
+      </c>
+      <c r="N9" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="O9" t="n">
+        <v>173855367025</v>
+      </c>
+      <c r="P9" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43</v>
-      </c>
-      <c r="G9" t="n">
-        <v>165</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O9" t="n">
-        <v>138316018885</v>
-      </c>
-      <c r="P9" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>48000</v>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>거래량 증가 및 타 종목 눈치보기 속 단기 상승 기대감 존재. 일부 하락 예측도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>['거래량', '단기 상승', '하락 예측']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1848000</v>
+        <v>1849000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.90%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G10" t="n">
-        <v>2204</v>
+        <v>2231</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1337,7 +1337,7 @@
         <v>1810000</v>
       </c>
       <c r="L10" t="n">
-        <v>1848000</v>
+        <v>1850000</v>
       </c>
       <c r="M10" t="n">
         <v>1805000</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3384713627000</v>
+        <v>3496728023500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,23 +1355,23 @@
         <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>212000</v>
+        <v>416000</v>
       </c>
       <c r="S10" t="n">
-        <v>69000</v>
+        <v>116000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 순매수 전환 및 자사주 매입 시작 소식에 따른 220만까지 상승 전망. 장기 투자 시 수익 기대.</t>
+          <t>외인 순매수 전환 및 자사주 매입 시작으로 190~200만원 돌파 기대감 고조. 장기 투자 긍정론.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 순매수', '자사주 매입', '장기 투자']</t>
+          <t>['외인 순매수', '자사주 매입', '목표가 200만']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,79 +1391,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13780</v>
+        <v>11050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.38%</t>
+          <t>'+4.15%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>530</v>
+        <v>194</v>
       </c>
       <c r="H11" t="n">
-        <v>4.92</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13330</v>
+        <v>10610</v>
       </c>
       <c r="K11" t="n">
-        <v>13600</v>
+        <v>10730</v>
       </c>
       <c r="L11" t="n">
-        <v>14030</v>
+        <v>12390</v>
       </c>
       <c r="M11" t="n">
-        <v>13210</v>
+        <v>10510</v>
       </c>
       <c r="N11" t="n">
-        <v>4.99</v>
+        <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>58155220995</v>
+        <v>112638607770</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>14350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>465</v>
       </c>
       <c r="R11" t="n">
-        <v>68000</v>
+        <v>46000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>기자회견 결과에 따른 기대감과 실망감이 교차. 호남 반도체 관련 언급 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['기자회견', '호남 반도체', '기대감']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10960</v>
+        <v>261000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>449</v>
       </c>
       <c r="G12" t="n">
-        <v>179</v>
+        <v>1947</v>
       </c>
       <c r="H12" t="n">
-        <v>12.5</v>
+        <v>46.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10610</v>
+        <v>252500</v>
       </c>
       <c r="K12" t="n">
-        <v>10730</v>
+        <v>261000</v>
       </c>
       <c r="L12" t="n">
-        <v>12390</v>
+        <v>261500</v>
       </c>
       <c r="M12" t="n">
-        <v>10510</v>
+        <v>257500</v>
       </c>
       <c r="N12" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>111886482755</v>
+        <v>1914403863000</v>
       </c>
       <c r="P12" t="n">
-        <v>14350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>465</v>
+        <v>78600</v>
       </c>
       <c r="R12" t="n">
-        <v>30000</v>
+        <v>-1310000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 매수세와 더불어 기자회견 내용 관련 불확실성 언급. 전기 전선주 장세에 대한 기대.</t>
+          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외국인', '기자회견', '전기 전선주']</t>
+          <t>['정치', '기자회견', '논쟁']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260750</v>
+        <v>17830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+3.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>452</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>1980</v>
+        <v>162</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>0.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>17250</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>17920</v>
       </c>
       <c r="L13" t="n">
-        <v>261500</v>
+        <v>18440</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>17450</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1854385728000</v>
+        <v>78626962180</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>-601000</v>
+        <v>-123000</v>
       </c>
       <c r="S13" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치 관련 내용으로 도배되어 있어 투자 관련 정보 부재. 비판적 정치 논평.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 기대감 형성. AI, 양자, 보안 관련 테마 연계.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '비판']</t>
+          <t>['양자컴퓨터', 'AI', '보안']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17770</v>
+        <v>13770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.27</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>156</v>
+        <v>532</v>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
+        <v>4.92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17250</v>
+        <v>13330</v>
       </c>
       <c r="K14" t="n">
-        <v>17920</v>
+        <v>13600</v>
       </c>
       <c r="L14" t="n">
-        <v>18440</v>
+        <v>14030</v>
       </c>
       <c r="M14" t="n">
-        <v>17450</v>
+        <v>13210</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>4.99</v>
       </c>
       <c r="O14" t="n">
-        <v>75058484190</v>
+        <v>58697092710</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-137000</v>
+        <v>231000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 기대감, AI/양자/보안 테마 관심.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', 'AI', '보안']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52300</v>
+        <v>18910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="H15" t="n">
-        <v>38.54</v>
+        <v>10.74</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51100</v>
+        <v>18490</v>
       </c>
       <c r="K15" t="n">
-        <v>51600</v>
+        <v>18900</v>
       </c>
       <c r="L15" t="n">
-        <v>55200</v>
+        <v>19700</v>
       </c>
       <c r="M15" t="n">
-        <v>51500</v>
+        <v>18760</v>
       </c>
       <c r="N15" t="n">
-        <v>38.62</v>
+        <v>10.85</v>
       </c>
       <c r="O15" t="n">
-        <v>207216844150</v>
+        <v>115664290655</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>499000</v>
+        <v>365000</v>
       </c>
       <c r="S15" t="n">
-        <v>123000</v>
+        <v>134000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 외인/기관의 집중 매수세 확인. 물량 소화 및 우상향 추세 전망. 일부 매물대 소화 과정 관찰.</t>
+          <t>미국 원전주 상승 및 중동 전쟁 관련 이슈로 주가 상승 기대. 대차해지 운동 활발.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외인/기관 매수', '우상향 추세', '물량 소화']</t>
+          <t>['원전주', '중동 전쟁', '대차해지']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18870</v>
+        <v>52200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.06%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="H16" t="n">
-        <v>10.74</v>
+        <v>38.54</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18490</v>
+        <v>51100</v>
       </c>
       <c r="K16" t="n">
-        <v>18900</v>
+        <v>51600</v>
       </c>
       <c r="L16" t="n">
-        <v>19700</v>
+        <v>55200</v>
       </c>
       <c r="M16" t="n">
-        <v>18760</v>
+        <v>51500</v>
       </c>
       <c r="N16" t="n">
-        <v>10.85</v>
+        <v>38.62</v>
       </c>
       <c r="O16" t="n">
-        <v>114281475135</v>
+        <v>212242081500</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R16" t="n">
-        <v>392000</v>
+        <v>442000</v>
       </c>
       <c r="S16" t="n">
-        <v>106000</v>
+        <v>231000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국장 원전주 상승세 및 중동 전쟁 관련 이슈 언급. 대차해지 운동을 통한 주가 방어 강조.</t>
+          <t>주가 상승에 대한 기대감과 함께 외인/기관의 집중 매수세 확인. 물량 소화 및 우상향 추세 전망. 일부 매물대 소화 과정 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전주', '중동 전쟁', '대차해지']</t>
+          <t>['외인/기관 매수', '우상향 추세', '물량 소화']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85600</v>
+        <v>13425</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>249</v>
+        <v>95</v>
       </c>
       <c r="F17" t="n">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>1128</v>
+        <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K17" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M17" t="n">
-        <v>85100</v>
+        <v>13280</v>
       </c>
       <c r="N17" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>102192988350</v>
+        <v>40092012095</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-206000</v>
+        <v>-78000</v>
       </c>
       <c r="S17" t="n">
-        <v>-59000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>뉴욕증시 원전주 급등 및 대미 투자 발표 기대감으로 인한 상승세. 연기금 매도 중.</t>
+          <t>호남 반도체 관련 불확실성으로 인한 주가 하락 및 투자자들의 실망감 표출. 매도 권유.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '연기금']</t>
+          <t>['호남 반도체', '주가 하락', '매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13370</v>
+        <v>85400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>254</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="G18" t="n">
-        <v>303</v>
+        <v>1143</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L18" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M18" t="n">
-        <v>13310</v>
+        <v>85100</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>38848586325</v>
+        <v>104286802050</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-447000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 불확실성으로 인한 주가 하락 및 투자자들의 실망감 표출. 매도 권유.</t>
+          <t>뉴욕증시 원전주 급등 및 대미 투자 관련 발표 가능성으로 주가 상승 기대. 연기금 매도세 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체', '주가 하락', '매도']</t>
+          <t>['원전주', '대미 투자', '연기금']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F19" t="n">
         <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="H19" t="n">
         <v>0.98</v>
@@ -2174,7 +2174,7 @@
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>76056926650</v>
+        <v>76550349305</v>
       </c>
       <c r="P19" t="n">
         <v>21100</v>
@@ -2186,20 +2186,20 @@
         <v>32000</v>
       </c>
       <c r="S19" t="n">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>락업 해제 물량 출회 및 주포의 움직임에 대한 부정적 언급. 단기 매매 권유 및 바이오 섹터의 특성 지적.</t>
+          <t>락업 해제 물량 부담 및 주포의 매매 패턴 의문으로 인한 주가 하락 우려. 바이오 대세장 속 개별 이슈.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['락업 해제', '주포', '단기 매매']</t>
+          <t>['락업 해제', '주포', '바이오']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10160</v>
+        <v>10140</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-3.43%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
         <v>1.24</v>
@@ -2266,7 +2266,7 @@
         <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>31290863975</v>
+        <v>31639925685</v>
       </c>
       <c r="P20" t="n">
         <v>15960</v>
@@ -2275,7 +2275,7 @@
         <v>3500</v>
       </c>
       <c r="R20" t="n">
-        <v>-20000</v>
+        <v>-117000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4175</v>
+        <v>4205</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.92%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" t="n">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="H21" t="n">
         <v>0.55</v>
@@ -2358,7 +2358,7 @@
         <v>0.95</v>
       </c>
       <c r="O21" t="n">
-        <v>35372917061</v>
+        <v>35823500850</v>
       </c>
       <c r="P21" t="n">
         <v>6900</v>
@@ -2367,7 +2367,7 @@
         <v>1738</v>
       </c>
       <c r="R21" t="n">
-        <v>-85000</v>
+        <v>-93000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2418,13 +2418,13 @@
         <v>-0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H22" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_13.xlsx
+++ b/data/trending_integrated_20260918_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26225</v>
+        <v>26850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.41%</t>
+          <t>'+24.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F2" t="n">
         <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>305627923650</v>
+        <v>314440159650</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8130</v>
+        <v>8200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.81%</t>
+          <t>'+16.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>147933866255</v>
+        <v>149022634480</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주가 상승과 하락에 대한 상반된 전망 제시. 공시 내용 분석 시도 및 보유 권유.</t>
+          <t>홀딩 의사 표명. 9월 14일 공시 내용 주목. 외국인 순매수 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주가 전망', '공시', '보유']</t>
+          <t>['공시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18540</v>
+        <v>18720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.94%</t>
+          <t>'+16.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F4" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G4" t="n">
-        <v>2268</v>
+        <v>2290</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>746559047610</v>
+        <v>759262084460</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31150</v>
+        <v>31200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.07%</t>
+          <t>'+10.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>187164534850</v>
+        <v>189069387125</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 기대감 형성. 프로그램 매수세와 함께 추세 전환 가능성 탐색.</t>
+          <t>가온전선과의 비교 언급. 저평가 해소 기대감과 단기 차익 실현 의지 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '가온전선', '프로그램매수']</t>
+          <t>['저평가 해소']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12650</v>
+        <v>12730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.24%</t>
+          <t>'+9.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
@@ -978,7 +978,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>120678121875</v>
+        <v>121248081900</v>
       </c>
       <c r="P6" t="n">
         <v>21150</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>셀그램 뉴스 기대감 있으나, 외인/기관 동시 매수세 약화 및 매도세 출현으로 하락 우려.</t>
+          <t>양극단 의견 대립. 일부 투자자 손실 및 탈출 의사. 단기 급등 기대감 및 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['셀그램', '외인/기관 매매', '하락 우려']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6390</v>
+        <v>6370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.67%</t>
+          <t>'+8.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
         <v>184</v>
@@ -1070,7 +1070,7 @@
         <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>87809732305</v>
+        <v>88255502470</v>
       </c>
       <c r="P7" t="n">
         <v>11760</v>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13930</v>
+        <v>11080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.32%</t>
+          <t>'+8.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>98</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>163</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>10250</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11500</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10230</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="O8" t="n">
+        <v>179175306380</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>78</v>
-      </c>
-      <c r="F8" t="n">
-        <v>44</v>
-      </c>
-      <c r="G8" t="n">
-        <v>165</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M8" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O8" t="n">
-        <v>139166667265</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R8" t="n">
-        <v>110000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>48000</v>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>감정적인 상승 기대감 표출. 일부 투자자 단기 차익 실현 의지. 외인 물량에 대한 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11100</v>
+        <v>13860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.29%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H9" t="n">
-        <v>18.13</v>
+        <v>2.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10250</v>
+        <v>12860</v>
       </c>
       <c r="K9" t="n">
-        <v>10280</v>
+        <v>13020</v>
       </c>
       <c r="L9" t="n">
-        <v>11500</v>
+        <v>14230</v>
       </c>
       <c r="M9" t="n">
-        <v>10230</v>
+        <v>13000</v>
       </c>
       <c r="N9" t="n">
-        <v>18.42</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>173855367025</v>
+        <v>140002836005</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>20300</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>2885</v>
       </c>
       <c r="R9" t="n">
-        <v>33000</v>
+        <v>110000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>거래량 증가 및 타 종목 눈치보기 속 단기 상승 기대감 존재. 일부 하락 예측도 공존.</t>
+          <t>미국 LA 전력청 관련 수주 기대감. 미주 매출 폭증 언급. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['거래량', '단기 상승', '하락 예측']</t>
+          <t>['미주 매출', '수주 기대']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="G10" t="n">
-        <v>2231</v>
+        <v>2277</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1337,7 +1337,7 @@
         <v>1810000</v>
       </c>
       <c r="L10" t="n">
-        <v>1850000</v>
+        <v>1851000</v>
       </c>
       <c r="M10" t="n">
         <v>1805000</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3496728023500</v>
+        <v>3667015406500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 순매수 전환 및 자사주 매입 시작으로 190~200만원 돌파 기대감 고조. 장기 투자 긍정론.</t>
+          <t>외인 순매수 및 자사주 매입 동시 진행. 목표가 상향 조정. 장기 투자 수익 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 순매수', '자사주 매입', '목표가 200만']</t>
+          <t>['외인 순매수', '자사주 매입']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11050</v>
+        <v>11010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.15%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
         <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H11" t="n">
         <v>12.5</v>
@@ -1438,7 +1438,7 @@
         <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>112638607770</v>
+        <v>113306037640</v>
       </c>
       <c r="P11" t="n">
         <v>14350</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>261000</v>
+        <v>13810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.37%</t>
+          <t>'+3.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>449</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>1947</v>
+        <v>538</v>
       </c>
       <c r="H12" t="n">
-        <v>46.48</v>
+        <v>4.92</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>252500</v>
+        <v>13330</v>
       </c>
       <c r="K12" t="n">
-        <v>261000</v>
+        <v>13600</v>
       </c>
       <c r="L12" t="n">
-        <v>261500</v>
+        <v>14030</v>
       </c>
       <c r="M12" t="n">
-        <v>257500</v>
+        <v>13210</v>
       </c>
       <c r="N12" t="n">
-        <v>46.52</v>
+        <v>4.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1914403863000</v>
+        <v>59198112575</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>78600</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-1310000</v>
+        <v>231000</v>
       </c>
       <c r="S12" t="n">
-        <v>717000</v>
+        <v>3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,103 +1555,103 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '논쟁']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17830</v>
+        <v>260250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.36%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>456</v>
       </c>
       <c r="G13" t="n">
-        <v>162</v>
+        <v>1977</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>46.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17250</v>
+        <v>252500</v>
       </c>
       <c r="K13" t="n">
-        <v>17920</v>
+        <v>261000</v>
       </c>
       <c r="L13" t="n">
-        <v>18440</v>
+        <v>261500</v>
       </c>
       <c r="M13" t="n">
-        <v>17450</v>
+        <v>257500</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>78626962180</v>
+        <v>2004825478500</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>78600</v>
       </c>
       <c r="R13" t="n">
-        <v>-123000</v>
+        <v>-1310000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 기대감 형성. AI, 양자, 보안 관련 테마 연계.</t>
+          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', 'AI', '보안']</t>
+          <t>['정치', '기자회견', '논쟁']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13770</v>
+        <v>17690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>532</v>
+        <v>170</v>
       </c>
       <c r="H14" t="n">
-        <v>4.92</v>
+        <v>0.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13330</v>
+        <v>17250</v>
       </c>
       <c r="K14" t="n">
-        <v>13600</v>
+        <v>17920</v>
       </c>
       <c r="L14" t="n">
-        <v>14030</v>
+        <v>18440</v>
       </c>
       <c r="M14" t="n">
-        <v>13210</v>
+        <v>17450</v>
       </c>
       <c r="N14" t="n">
-        <v>4.99</v>
+        <v>0.7</v>
       </c>
       <c r="O14" t="n">
-        <v>58697092710</v>
+        <v>80381093450</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>30550</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>6100</v>
       </c>
       <c r="R14" t="n">
-        <v>231000</v>
+        <v>-123000</v>
       </c>
       <c r="S14" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 국내 관련주 주목. 공공기관 보안 관련 기대감 있으나, 주가 상승 여부는 불확실.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['양자컴퓨터', '보안주', 'AI반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18910</v>
+        <v>18895</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
         <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H15" t="n">
         <v>10.74</v>
@@ -1806,7 +1806,7 @@
         <v>10.85</v>
       </c>
       <c r="O15" t="n">
-        <v>115664290655</v>
+        <v>117456755425</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전주 상승 및 중동 전쟁 관련 이슈로 주가 상승 기대. 대차해지 운동 활발.</t>
+          <t>대차해지 운동 언급. 수주 발표 후 주가 하락에 대한 의문 표출. 하반기 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전주', '중동 전쟁', '대차해지']</t>
+          <t>['대차해지', '수주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H16" t="n">
         <v>38.54</v>
@@ -1898,7 +1898,7 @@
         <v>38.62</v>
       </c>
       <c r="O16" t="n">
-        <v>212242081500</v>
+        <v>214565015350</v>
       </c>
       <c r="P16" t="n">
         <v>67300</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13425</v>
+        <v>85500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="G17" t="n">
-        <v>307</v>
+        <v>1173</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L17" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M17" t="n">
-        <v>13280</v>
+        <v>85100</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O17" t="n">
-        <v>40092012095</v>
+        <v>105754578300</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-78000</v>
+        <v>-447000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 불확실성으로 인한 주가 하락 및 투자자들의 실망감 표출. 매도 권유.</t>
+          <t>뉴욕증시 원전주 급등 및 대미 투자 관련 발표 가능성으로 주가 상승 기대. 연기금 매도세 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['호남 반도체', '주가 하락', '매도']</t>
+          <t>['원전주', '대미 투자', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85400</v>
+        <v>13370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>254</v>
+        <v>99</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>1143</v>
+        <v>331</v>
       </c>
       <c r="H18" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K18" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L18" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M18" t="n">
-        <v>85100</v>
+        <v>13280</v>
       </c>
       <c r="N18" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>104286802050</v>
+        <v>40390221050</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-447000</v>
+        <v>-78000</v>
       </c>
       <c r="S18" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>뉴욕증시 원전주 급등 및 대미 투자 관련 발표 가능성으로 주가 상승 기대. 연기금 매도세 우려.</t>
+          <t>호남 반도체 관련 불확실성 언급. 일부 투자자 차익 실현 및 급락 경고.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '연기금']</t>
+          <t>['호남 반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17850</v>
+        <v>17760</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="H19" t="n">
         <v>0.98</v>
@@ -2174,7 +2174,7 @@
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>76550349305</v>
+        <v>77207898320</v>
       </c>
       <c r="P19" t="n">
         <v>21100</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>락업 해제 물량 부담 및 주포의 매매 패턴 의문으로 인한 주가 하락 우려. 바이오 대세장 속 개별 이슈.</t>
+          <t>보호예수 해제 물량 우려 속 주가 하락. 3상 진행 및 바이오 대세장 기대감 존재하나, 주포의 움직임에 대한 의구심.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['락업 해제', '주포', '바이오']</t>
+          <t>['락업해제', '주포', '보호예수']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10140</v>
+        <v>10170</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.43%</t>
+          <t>'-3.14%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H20" t="n">
         <v>1.24</v>
@@ -2266,7 +2266,7 @@
         <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>31639925685</v>
+        <v>31899734320</v>
       </c>
       <c r="P20" t="n">
         <v>15960</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4205</v>
+        <v>4195</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-9.49%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F21" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G21" t="n">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="H21" t="n">
         <v>0.55</v>
@@ -2358,7 +2358,7 @@
         <v>0.95</v>
       </c>
       <c r="O21" t="n">
-        <v>35823500850</v>
+        <v>36044922120</v>
       </c>
       <c r="P21" t="n">
         <v>6900</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재, 스테이블코인 테마 편입 가능성.</t>
+          <t>STO 사업 추진 및 코인 관련 호재 언급. 주포 물량 넘김 및 탈출 경고.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['STO', '암호화폐', '스테이블코인']</t>
+          <t>['STO', '코인']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H22" t="n">
         <v>3.69</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>회사의 지분 보유 및 기술 개발 등 긍정적 요소 언급에도 불구하고, 낮은 주가와 거래량에 대한 불만 토로. 매도 의견.</t>
+          <t>K-OTC 거래 및 지분 보유 관련 기대감. 액면가 대비 고평가 논란 및 매도 압력.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['지분 보유', '기술 개발', '매도']</t>
+          <t>['K-OTC', '지분 보유']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20260918_13.xlsx
+++ b/data/trending_integrated_20260918_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26850</v>
+        <v>27500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.31%</t>
+          <t>'+27.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>26850</v>
+        <v>28050</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>314440159650</v>
+        <v>370824951350</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>외인 폭풍 매수 및 프로그램 매수세 유입으로 강한 상승세. 통신주 대비 저평가 분석.</t>
+          <t>프로그램 폭풍 매수 및 업황/실적 성장성 기반 긍정적 전망. 미래 SK하이닉스 비유.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['외인 매수', '프로그램 매수', '상승세']</t>
+          <t>['업황', '실적성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8200</v>
+        <v>8170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.81%</t>
+          <t>'+16.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>149022634480</v>
+        <v>149587602160</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>홀딩 의사 표명. 9월 14일 공시 내용 주목. 외국인 순매수 관찰.</t>
+          <t>공시 내용 언급 있으나, 뚜렷한 방향성 없이 주가 등락에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18720</v>
+        <v>18770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.06%</t>
+          <t>'+16.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F4" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G4" t="n">
-        <v>2290</v>
+        <v>2335</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>759262084460</v>
+        <v>773507112080</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관 동시 매수세 확인된 가운데 2차 매물대 돌파 시도. 숏커버링 발생 및 20,000원 돌파 기대감 고조.</t>
+          <t>외인/기관/투신 매수세 집중 및 숏커버링 발생으로 인한 강한 상승세 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외인기관', '매물대돌파', '숏커버링']</t>
+          <t>['외인기관', '숏커버링']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31200</v>
+        <v>31150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.25%</t>
+          <t>'+10.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
         <v>66</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>189069387125</v>
+        <v>190612167125</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12730</v>
+        <v>6430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.93%</t>
+          <t>'+9.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>648</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
-        <v>8.029999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11580</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>12200</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>13820</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>12100</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>8.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>121248081900</v>
+        <v>89031697340</v>
       </c>
       <c r="P6" t="n">
-        <v>21150</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>8140</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>349000</v>
+        <v>733000</v>
       </c>
       <c r="S6" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>양극단 의견 대립. 일부 투자자 손실 및 탈출 의사. 단기 급등 기대감 및 경고.</t>
+          <t>전환사채 발행 가능성 및 박스권 돌파 기대감 언급. 외국인/프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['전환사채', '박스권돌파']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6370</v>
+        <v>12660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+9.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="G7" t="n">
-        <v>184</v>
+        <v>661</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5880</v>
+        <v>11580</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>12200</v>
       </c>
       <c r="L7" t="n">
-        <v>6920</v>
+        <v>13820</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>12100</v>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>88255502470</v>
+        <v>121857461195</v>
       </c>
       <c r="P7" t="n">
-        <v>11760</v>
+        <v>21150</v>
       </c>
       <c r="Q7" t="n">
-        <v>1620</v>
+        <v>8140</v>
       </c>
       <c r="R7" t="n">
-        <v>733000</v>
+        <v>349000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 전력/변압기 관련 사업 성장 기대감. 전환사채 발행 예정.</t>
+          <t>셀그램 관련 뉴스 및 외인/기관 동시 매수 언급 있으나, 주가 하락 및 손실 관련 부정적 의견 우세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '전력', '변압기']</t>
+          <t>['셀그램', '외인기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11080</v>
+        <v>11120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.10%</t>
+          <t>'+8.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="H8" t="n">
         <v>18.13</v>
@@ -1162,7 +1162,7 @@
         <v>18.42</v>
       </c>
       <c r="O8" t="n">
-        <v>179175306380</v>
+        <v>184359281275</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>감정적인 상승 기대감 표출. 일부 투자자 단기 차익 실현 의지. 외인 물량에 대한 언급.</t>
+          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13860</v>
+        <v>13900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.78%</t>
+          <t>'+8.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
         <v>2.83</v>
@@ -1254,7 +1254,7 @@
         <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>140002836005</v>
+        <v>140764391665</v>
       </c>
       <c r="P9" t="n">
         <v>20300</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 관련 수주 기대감. 미주 매출 폭증 언급. 매집 정황 포착.</t>
+          <t>미국 LA 전력청 수주 기대감 및 매출 증대 뉴스 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미주 매출', '수주 기대']</t>
+          <t>['LA전력청', '매출증대']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G10" t="n">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3667015406500</v>
+        <v>3774985609000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11010</v>
+        <v>11105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H11" t="n">
         <v>12.5</v>
@@ -1438,7 +1438,7 @@
         <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>113306037640</v>
+        <v>114533227095</v>
       </c>
       <c r="P11" t="n">
         <v>14350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기자회견 결과에 따른 기대감과 실망감이 교차. 호남 반도체 관련 언급 기대.</t>
+          <t>호남 반도체 관련 기대감 언급 있으나, 구체적 내용 부재 및 부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기자회견', '호남 반도체', '기대감']</t>
+          <t>['호남반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13810</v>
+        <v>13860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.60%</t>
+          <t>'+3.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="H12" t="n">
         <v>4.92</v>
@@ -1530,7 +1530,7 @@
         <v>4.99</v>
       </c>
       <c r="O12" t="n">
-        <v>59198112575</v>
+        <v>59781996825</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G13" t="n">
-        <v>1977</v>
+        <v>1943</v>
       </c>
       <c r="H13" t="n">
         <v>46.48</v>
@@ -1622,7 +1622,7 @@
         <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>2004825478500</v>
+        <v>2061742261250</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1667,70 +1667,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17690</v>
+        <v>18940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>170</v>
+        <v>438</v>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17250</v>
+        <v>18490</v>
       </c>
       <c r="K14" t="n">
-        <v>17920</v>
+        <v>18900</v>
       </c>
       <c r="L14" t="n">
-        <v>18440</v>
+        <v>19700</v>
       </c>
       <c r="M14" t="n">
-        <v>17450</v>
+        <v>18760</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>80381093450</v>
+        <v>119094821530</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-123000</v>
+        <v>365000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>134000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 국내 관련주 주목. 공공기관 보안 관련 기대감 있으나, 주가 상승 여부는 불확실.</t>
+          <t>대차해지 운동 언급. 수주 발표 후 주가 하락에 대한 의문 표출. 하반기 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', 'AI반도체']</t>
+          <t>['대차해지', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18895</v>
+        <v>52300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H15" t="n">
-        <v>10.74</v>
+        <v>38.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18490</v>
+        <v>51100</v>
       </c>
       <c r="K15" t="n">
-        <v>18900</v>
+        <v>51600</v>
       </c>
       <c r="L15" t="n">
-        <v>19700</v>
+        <v>55200</v>
       </c>
       <c r="M15" t="n">
-        <v>18760</v>
+        <v>51500</v>
       </c>
       <c r="N15" t="n">
-        <v>10.85</v>
+        <v>38.62</v>
       </c>
       <c r="O15" t="n">
-        <v>117456755425</v>
+        <v>216583996650</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>365000</v>
+        <v>442000</v>
       </c>
       <c r="S15" t="n">
-        <v>134000</v>
+        <v>231000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차해지 운동 언급. 수주 발표 후 주가 하락에 대한 의문 표출. 하반기 상승 기대.</t>
+          <t>외인/기관 매수세 및 시장 관심 증가에 따른 긍정적 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '수주']</t>
+          <t>['외인기관', '시장관심']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52200</v>
+        <v>17630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>421</v>
+        <v>172</v>
       </c>
       <c r="H16" t="n">
-        <v>38.54</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>51100</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>51600</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>55200</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>51500</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
-        <v>38.62</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>214565015350</v>
+        <v>81208154330</v>
       </c>
       <c r="P16" t="n">
-        <v>67300</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>23150</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>442000</v>
+        <v>-123000</v>
       </c>
       <c r="S16" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 외인/기관의 집중 매수세 확인. 물량 소화 및 우상향 추세 전망. 일부 매물대 소화 과정 관찰.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 국내 관련주 주목. 공공기관 보안 관련 기대감 있으나, 주가 상승 여부는 불확실.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인/기관 매수', '우상향 추세', '물량 소화']</t>
+          <t>['양자컴퓨터', '보안주', 'AI반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85500</v>
+        <v>13390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="F17" t="n">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>1173</v>
+        <v>334</v>
       </c>
       <c r="H17" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K17" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M17" t="n">
-        <v>85100</v>
+        <v>13280</v>
       </c>
       <c r="N17" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>105754578300</v>
+        <v>40722041695</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-447000</v>
+        <v>-78000</v>
       </c>
       <c r="S17" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>뉴욕증시 원전주 급등 및 대미 투자 관련 발표 가능성으로 주가 상승 기대. 연기금 매도세 우려.</t>
+          <t>호남 반도체 관련 불확실성 언급. 일부 투자자 차익 실현 및 급락 경고.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '연기금']</t>
+          <t>['호남 반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13370</v>
+        <v>85500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>260</v>
       </c>
       <c r="F18" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="G18" t="n">
-        <v>331</v>
+        <v>1197</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L18" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M18" t="n">
-        <v>13280</v>
+        <v>85100</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>40390221050</v>
+        <v>106687300200</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-78000</v>
+        <v>-447000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 불확실성 언급. 일부 투자자 차익 실현 및 급락 경고.</t>
+          <t>미국 원전주 급등 소식과 대미 투자 관련 발표 가능성에 대한 기대감으로 주가 상승 움직임을 보이고 있으며, GPU 전력 부족 뉴스도 긍정적 요인으로 작용.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체']</t>
+          <t>['원전주', '대미투자', '뉴스케일']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17760</v>
+        <v>17600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-1.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H19" t="n">
         <v>0.98</v>
@@ -2168,13 +2168,13 @@
         <v>20400</v>
       </c>
       <c r="M19" t="n">
-        <v>17670</v>
+        <v>17580</v>
       </c>
       <c r="N19" t="n">
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>77207898320</v>
+        <v>78110438800</v>
       </c>
       <c r="P19" t="n">
         <v>21100</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 우려 속 주가 하락. 3상 진행 및 바이오 대세장 기대감 존재하나, 주포의 움직임에 대한 의구심.</t>
+          <t>머크 3상 진행 속도와 바이오 대세장 기대감 속에서 락업 해제 물량 소화 중이라는 의견과 함께 주포의 움직임에 주목하고 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['락업해제', '주포', '보호예수']</t>
+          <t>['락업해제', '주포', '3상']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10170</v>
+        <v>10130</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.14%</t>
+          <t>'-3.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H20" t="n">
         <v>1.24</v>
@@ -2266,7 +2266,7 @@
         <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>31899734320</v>
+        <v>32293956230</v>
       </c>
       <c r="P20" t="n">
         <v>15960</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4195</v>
+        <v>4170</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.49%</t>
+          <t>'-10.03%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F21" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G21" t="n">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="H21" t="n">
         <v>0.55</v>
@@ -2358,7 +2358,7 @@
         <v>0.95</v>
       </c>
       <c r="O21" t="n">
-        <v>36044922120</v>
+        <v>36450435669</v>
       </c>
       <c r="P21" t="n">
         <v>6900</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-39.53%</t>
+          <t>'-46.51%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H22" t="n">
         <v>3.69</v>
@@ -2444,19 +2444,19 @@
         <v>44</v>
       </c>
       <c r="M22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
         <v>3.71</v>
       </c>
       <c r="O22" t="n">
-        <v>166088829</v>
+        <v>173053965</v>
       </c>
       <c r="P22" t="n">
         <v>901</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R22" t="n">
         <v>-58000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>K-OTC 거래 및 지분 보유 관련 기대감. 액면가 대비 고평가 논란 및 매도 압력.</t>
+          <t>장외 주식 및 대주주 관련 기대감 있으나, 주가 하락 지속 및 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['K-OTC', '지분 보유']</t>
+          <t>['장외주식', '대주주']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20260918_13.xlsx
+++ b/data/trending_integrated_20260918_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>370824951350</v>
+        <v>382280612550</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8170</v>
+        <v>8160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.38%</t>
+          <t>'+16.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>149587602160</v>
+        <v>150743583140</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18770</v>
+        <v>18640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.37%</t>
+          <t>'+15.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F4" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G4" t="n">
-        <v>2335</v>
+        <v>2393</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>773507112080</v>
+        <v>782166657365</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관/투신 매수세 집중 및 숏커버링 발생으로 인한 강한 상승세 기대.</t>
+          <t>텍사스 관련 긍정적 뉴스와 함께 18,000원 돌파 및 20,000원 돌파 기대감이 높으며, 숏커버링 발생 및 거래량 증가에 대한 분석 포함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외인기관', '숏커버링']</t>
+          <t>['텍사스', '숏커버링', '거래량 증가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31150</v>
+        <v>31250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.07%</t>
+          <t>'+10.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
         <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>190612167125</v>
+        <v>192323339600</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6430</v>
+        <v>6480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.35%</t>
+          <t>'+10.20%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H6" t="n">
         <v>2.85</v>
@@ -978,7 +978,7 @@
         <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>89031697340</v>
+        <v>89682356880</v>
       </c>
       <c r="P6" t="n">
         <v>11760</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>전환사채 발행 가능성 및 박스권 돌파 기대감 언급. 외국인/프로그램 매수세 확인.</t>
+          <t>박스권 돌파 및 변압기 관련 긍정적 전망과 함께 26년도 매출액 및 영업이익 예상치가 제시되었으며, 외국인 순매수 동향도 긍정적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['전환사채', '박스권돌파']</t>
+          <t>['박스권 돌파', '변압기', '매출액 예상']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12660</v>
+        <v>12620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.33%</t>
+          <t>'+8.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F7" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G7" t="n">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="H7" t="n">
         <v>8.029999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>121857461195</v>
+        <v>122440029635</v>
       </c>
       <c r="P7" t="n">
         <v>21150</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11120</v>
+        <v>13910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.49%</t>
+          <t>'+8.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
-        <v>18.13</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10250</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>10280</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>11500</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>10230</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>18.42</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>184359281275</v>
+        <v>141430980905</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>33000</v>
+        <v>110000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
+          <t>미주 매출 3.5배 증가 및 LA전력청 공급 테스트 완료 소식과 함께 14,000원 돌파 기대감이 있으나, 일부 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['LA전력청', '미주 매출', '테스트 완료']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13900</v>
+        <v>10980</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.09%</t>
+          <t>'+7.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>103</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>176</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10250</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10280</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10230</v>
+      </c>
+      <c r="N9" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="O9" t="n">
+        <v>188137012870</v>
+      </c>
+      <c r="P9" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>80</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44</v>
-      </c>
-      <c r="G9" t="n">
-        <v>179</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O9" t="n">
-        <v>140764391665</v>
-      </c>
-      <c r="P9" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R9" t="n">
-        <v>110000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>48000</v>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 수주 기대감 및 매출 증대 뉴스 기반 긍정적 전망.</t>
+          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출증대']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1849000</v>
+        <v>1846000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+5.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="G10" t="n">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="H10" t="n">
         <v>50.1</v>
@@ -1346,7 +1346,7 @@
         <v>50.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3774985609000</v>
+        <v>3851738038000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 순매수 및 자사주 매입 동시 진행. 목표가 상향 조정. 장기 투자 수익 기대.</t>
+          <t>외국인 순매수 전환 및 자사주 매입 시작에 따른 200만원 돌파 기대감이 높으며, 일본 금리 인상 영향은 없을 것이라는 분석 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 순매수', '자사주 매입']</t>
+          <t>['외국인 순매수', '자사주 매입', '200만원 목표']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,79 +1391,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11105</v>
+        <v>14030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+5.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>204</v>
+        <v>558</v>
       </c>
       <c r="H11" t="n">
-        <v>12.5</v>
+        <v>4.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10610</v>
+        <v>13330</v>
       </c>
       <c r="K11" t="n">
-        <v>10730</v>
+        <v>13600</v>
       </c>
       <c r="L11" t="n">
-        <v>12390</v>
+        <v>14050</v>
       </c>
       <c r="M11" t="n">
-        <v>10510</v>
+        <v>13210</v>
       </c>
       <c r="N11" t="n">
-        <v>12.6</v>
+        <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>114533227095</v>
+        <v>64526995170</v>
       </c>
       <c r="P11" t="n">
-        <v>14350</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>465</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>46000</v>
+        <v>231000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 기대감 언급 있으나, 구체적 내용 부재 및 부정적 의견 혼재.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['호남반도체']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,91 +1471,91 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13860</v>
+        <v>11100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+4.62%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>544</v>
+        <v>205</v>
       </c>
       <c r="H12" t="n">
-        <v>4.92</v>
+        <v>12.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13330</v>
+        <v>10610</v>
       </c>
       <c r="K12" t="n">
-        <v>13600</v>
+        <v>10730</v>
       </c>
       <c r="L12" t="n">
-        <v>14030</v>
+        <v>12390</v>
       </c>
       <c r="M12" t="n">
-        <v>13210</v>
+        <v>10510</v>
       </c>
       <c r="N12" t="n">
-        <v>4.99</v>
+        <v>12.6</v>
       </c>
       <c r="O12" t="n">
-        <v>59781996825</v>
+        <v>115364310470</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>14350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>465</v>
       </c>
       <c r="R12" t="n">
-        <v>231000</v>
+        <v>46000</v>
       </c>
       <c r="S12" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>호남 반도체 관련 기자회견에 대한 기대감이 있으나, 구체적인 내용 부재 및 부정적 전망이 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['호남 반도체', '기자회견', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,95 +1563,95 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260250</v>
+        <v>17770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+3.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>459</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>1943</v>
+        <v>168</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>0.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>17250</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>17920</v>
       </c>
       <c r="L13" t="n">
-        <v>261500</v>
+        <v>18440</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>17450</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2061742261250</v>
+        <v>82265278780</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>-1310000</v>
+        <v>-123000</v>
       </c>
       <c r="S13" t="n">
-        <v>717000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
+          <t>미국 양자컴퓨터주 급등 소식과 함께 20,000원 터치 가능성 및 공공기관 보안 관련 긍정적 전망이 있으나, 일부 하락 의견도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '논쟁']</t>
+          <t>['양자컴퓨터', '공공기관 보안', '20000원 돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18940</v>
+        <v>260000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>438</v>
+        <v>1926</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>46.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18490</v>
+        <v>252500</v>
       </c>
       <c r="K14" t="n">
-        <v>18900</v>
+        <v>261000</v>
       </c>
       <c r="L14" t="n">
-        <v>19700</v>
+        <v>261500</v>
       </c>
       <c r="M14" t="n">
-        <v>18760</v>
+        <v>257500</v>
       </c>
       <c r="N14" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>119094821530</v>
+        <v>2083279902750</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>78600</v>
       </c>
       <c r="R14" t="n">
-        <v>365000</v>
+        <v>-1310000</v>
       </c>
       <c r="S14" t="n">
-        <v>134000</v>
+        <v>717000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동 언급. 수주 발표 후 주가 하락에 대한 의문 표출. 하반기 상승 기대.</t>
+          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '수주']</t>
+          <t>['정치', '기자회견', '논쟁']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52300</v>
+        <v>52400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H15" t="n">
         <v>38.54</v>
@@ -1806,7 +1806,7 @@
         <v>38.62</v>
       </c>
       <c r="O15" t="n">
-        <v>216583996650</v>
+        <v>220826005400</v>
       </c>
       <c r="P15" t="n">
         <v>67300</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17630</v>
+        <v>18960</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
-        <v>172</v>
+        <v>438</v>
       </c>
       <c r="H16" t="n">
-        <v>0.97</v>
+        <v>10.74</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17250</v>
+        <v>18490</v>
       </c>
       <c r="K16" t="n">
-        <v>17920</v>
+        <v>18900</v>
       </c>
       <c r="L16" t="n">
-        <v>18440</v>
+        <v>19700</v>
       </c>
       <c r="M16" t="n">
-        <v>17450</v>
+        <v>18760</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>10.85</v>
       </c>
       <c r="O16" t="n">
-        <v>81208154330</v>
+        <v>121034808855</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-123000</v>
+        <v>365000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>134000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 국내 관련주 주목. 공공기관 보안 관련 기대감 있으나, 주가 상승 여부는 불확실.</t>
+          <t>미국 원전주 상승세와 더불어 하반기 상승 전망이 있으나, 수주 발표 이후 주가 하락에 대한 의문과 대차해지 운동 참여 독려가 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', 'AI반도체']</t>
+          <t>['미국 원전주', '하반기 전망', '대차해지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13390</v>
+        <v>85600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="G17" t="n">
-        <v>334</v>
+        <v>1239</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L17" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M17" t="n">
-        <v>13280</v>
+        <v>85100</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O17" t="n">
-        <v>40722041695</v>
+        <v>109421491250</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-78000</v>
+        <v>-447000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 불확실성 언급. 일부 투자자 차익 실현 및 급락 경고.</t>
+          <t>미국 원전주 급등 및 대미 투자 발표 가능성 뉴스에 따른 기대감 형성. 연기금 매도세는 부담 요인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['호남 반도체']</t>
+          <t>['원전주', '대미 투자', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85500</v>
+        <v>13390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>260</v>
+        <v>101</v>
       </c>
       <c r="F18" t="n">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>1197</v>
+        <v>341</v>
       </c>
       <c r="H18" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K18" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L18" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M18" t="n">
-        <v>85100</v>
+        <v>13280</v>
       </c>
       <c r="N18" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>106687300200</v>
+        <v>40933118220</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-447000</v>
+        <v>-78000</v>
       </c>
       <c r="S18" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 소식과 대미 투자 관련 발표 가능성에 대한 기대감으로 주가 상승 움직임을 보이고 있으며, GPU 전력 부족 뉴스도 긍정적 요인으로 작용.</t>
+          <t>호남 반도체 사업 진행 여부에 대한 기대와 부정적인 전망이 교차하며, 단기 급등 후 급락 가능성에 대한 우려가 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '뉴스케일']</t>
+          <t>['호남 반도체', '급등락', '기대감']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,191 +2120,191 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17600</v>
+        <v>10140</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.84%</t>
+          <t>'-3.43%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.38</v>
+        <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17930</v>
+        <v>10500</v>
       </c>
       <c r="K19" t="n">
-        <v>18400</v>
+        <v>10650</v>
       </c>
       <c r="L19" t="n">
-        <v>20400</v>
+        <v>10710</v>
       </c>
       <c r="M19" t="n">
-        <v>17580</v>
+        <v>10100</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>78110438800</v>
+        <v>32860812090</v>
       </c>
       <c r="P19" t="n">
-        <v>21100</v>
+        <v>15960</v>
       </c>
       <c r="Q19" t="n">
-        <v>9900</v>
+        <v>3500</v>
       </c>
       <c r="R19" t="n">
-        <v>32000</v>
+        <v>-117000</v>
       </c>
       <c r="S19" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머크 3상 진행 속도와 바이오 대세장 기대감 속에서 락업 해제 물량 소화 중이라는 의견과 함께 주포의 움직임에 주목하고 있음.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['락업해제', '주포', '3상']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10130</v>
+        <v>17300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'-3.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="G20" t="n">
-        <v>141</v>
+        <v>376</v>
       </c>
       <c r="H20" t="n">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10500</v>
+        <v>17930</v>
       </c>
       <c r="K20" t="n">
-        <v>10650</v>
+        <v>18400</v>
       </c>
       <c r="L20" t="n">
-        <v>10710</v>
+        <v>20400</v>
       </c>
       <c r="M20" t="n">
-        <v>10100</v>
+        <v>17270</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>32293956230</v>
+        <v>80015155520</v>
       </c>
       <c r="P20" t="n">
-        <v>15960</v>
+        <v>21100</v>
       </c>
       <c r="Q20" t="n">
-        <v>3500</v>
+        <v>9900</v>
       </c>
       <c r="R20" t="n">
-        <v>-117000</v>
+        <v>32000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>머크사의 3상 임상 진행 소식에도 불구하고 락업 해제 물량 부담 및 주가 하락 가능성에 대한 우려가 있으며, 단기 매매를 권장하는 의견이 다수.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['락업 해제', '머크 3상', '단기 매매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4170</v>
+        <v>4210</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-10.03%</t>
+          <t>'-9.17%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F21" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G21" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H21" t="n">
         <v>0.55</v>
@@ -2358,7 +2358,7 @@
         <v>0.95</v>
       </c>
       <c r="O21" t="n">
-        <v>36450435669</v>
+        <v>36649525244</v>
       </c>
       <c r="P21" t="n">
         <v>6900</v>
@@ -2418,13 +2418,13 @@
         <v>-0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
         <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H22" t="n">
         <v>3.69</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>장외 주식 및 대주주 관련 기대감 있으나, 주가 하락 지속 및 부정적 전망 우세.</t>
+          <t>장외 거래 및 대주주 변경 가능성에 대한 기대감과 함께, 현재 주가에 대한 부정적인 의견 및 개미 투자자들의 행태에 대한 비판이 공존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['장외주식', '대주주']</t>
+          <t>['장외 거래', '대주주 변경', '현재 주가']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20260918_13.xlsx
+++ b/data/trending_integrated_20260918_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F2" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>382280612550</v>
+        <v>396704191550</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>프로그램 폭풍 매수 및 업황/실적 성장성 기반 긍정적 전망. 미래 SK하이닉스 비유.</t>
+          <t>통신주 업황 및 실적 성장성 기반 폭풍 매수세 확인. 5~6만원대 재진입 및 SK하이닉스와 비교하며 높은 기대감 표출.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['업황', '실적성장성']</t>
+          <t>['통신주', '업황', '실적 성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8160</v>
+        <v>8130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.24%</t>
+          <t>'+15.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>150743583140</v>
+        <v>151852522115</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>공시 내용 언급 있으나, 뚜렷한 방향성 없이 주가 등락에 대한 기대와 우려 혼재.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공시']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18640</v>
+        <v>18650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.56%</t>
+          <t>'+15.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="F4" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G4" t="n">
-        <v>2393</v>
+        <v>2442</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>782166657365</v>
+        <v>791767628195</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31250</v>
+        <v>31300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.42%</t>
+          <t>'+10.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
         <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>192323339600</v>
+        <v>194135677900</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6480</v>
+        <v>6450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.20%</t>
+          <t>'+9.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H6" t="n">
         <v>2.85</v>
@@ -978,7 +978,7 @@
         <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>89682356880</v>
+        <v>90303310550</v>
       </c>
       <c r="P6" t="n">
         <v>11760</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 변압기 관련 긍정적 전망과 함께 26년도 매출액 및 영업이익 예상치가 제시되었으며, 외국인 순매수 동향도 긍정적.</t>
+          <t>전환사채 발행 가능성에도 불구하고 박스권 돌파 및 외국인 순매수 1위 기록. 2026년 매출 1조원 및 영업익 600억원 예상.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '변압기', '매출액 예상']</t>
+          <t>['전환사채', '외국인 순매수', '매출 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12620</v>
+        <v>12590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.98%</t>
+          <t>'+8.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G7" t="n">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="H7" t="n">
         <v>8.029999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>122440029635</v>
+        <v>123151767670</v>
       </c>
       <c r="P7" t="n">
         <v>21150</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 및 외인/기관 동시 매수 언급 있으나, 주가 하락 및 손실 관련 부정적 의견 우세.</t>
+          <t>외인/기관 동시 매수 언급 있으나, 전반적으로 하락 및 손실 우려, 모더나 관련 기대감 있으나 불확실성 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['셀그램', '외인기관']</t>
+          <t>['모더나', '외인/기관', '손실 우려']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13910</v>
+        <v>13900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.16%</t>
+          <t>'+8.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>141430980905</v>
+        <v>141969349105</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 증가 및 LA전력청 공급 테스트 완료 소식과 함께 14,000원 돌파 기대감이 있으나, 일부 부정적 의견도 존재.</t>
+          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '미주 매출', '테스트 완료']</t>
+          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10980</v>
+        <v>1849000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.12%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>456</v>
       </c>
       <c r="G9" t="n">
-        <v>176</v>
+        <v>2219</v>
       </c>
       <c r="H9" t="n">
-        <v>18.13</v>
+        <v>50.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10250</v>
+        <v>1745000</v>
       </c>
       <c r="K9" t="n">
-        <v>10280</v>
+        <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>11500</v>
+        <v>1851000</v>
       </c>
       <c r="M9" t="n">
-        <v>10230</v>
+        <v>1805000</v>
       </c>
       <c r="N9" t="n">
-        <v>18.42</v>
+        <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>188137012870</v>
+        <v>3965627455000</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>33000</v>
+        <v>416000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
+          <t>SK하이닉스의 목표 주가 상향 조정(200만원 이상) 및 외인/기관의 쌍끌이 매수세 확인. 장기 보유 시 수익 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SK하이닉스', '목표 주가', '외인/기관 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1846000</v>
+        <v>10830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.79%</t>
+          <t>'+5.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.29</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F10" t="n">
-        <v>443</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>2283</v>
+        <v>178</v>
       </c>
       <c r="H10" t="n">
-        <v>50.1</v>
+        <v>18.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1745000</v>
+        <v>10250</v>
       </c>
       <c r="K10" t="n">
-        <v>1810000</v>
+        <v>10280</v>
       </c>
       <c r="L10" t="n">
-        <v>1851000</v>
+        <v>11500</v>
       </c>
       <c r="M10" t="n">
-        <v>1805000</v>
+        <v>10230</v>
       </c>
       <c r="N10" t="n">
-        <v>50.2</v>
+        <v>18.42</v>
       </c>
       <c r="O10" t="n">
-        <v>3851738038000</v>
+        <v>192373344685</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>416000</v>
+        <v>33000</v>
       </c>
       <c r="S10" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 순매수 전환 및 자사주 매입 시작에 따른 200만원 돌파 기대감이 높으며, 일본 금리 인상 영향은 없을 것이라는 분석 제시.</t>
+          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '자사주 매입', '200만원 목표']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.25%</t>
+          <t>'+5.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>64526995170</v>
+        <v>66822735755</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11100</v>
+        <v>11030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.62%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H12" t="n">
         <v>12.5</v>
@@ -1530,7 +1530,7 @@
         <v>12.6</v>
       </c>
       <c r="O12" t="n">
-        <v>115364310470</v>
+        <v>116050387320</v>
       </c>
       <c r="P12" t="n">
         <v>14350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 기자회견에 대한 기대감이 있으나, 구체적인 내용 부재 및 부정적 전망이 혼재.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '기대감']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17770</v>
+        <v>19100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>168</v>
+        <v>448</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17250</v>
+        <v>18490</v>
       </c>
       <c r="K13" t="n">
-        <v>17920</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>18440</v>
+        <v>19700</v>
       </c>
       <c r="M13" t="n">
-        <v>17450</v>
+        <v>18760</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>82265278780</v>
+        <v>123362943975</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-123000</v>
+        <v>365000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>134000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등 소식과 함께 20,000원 터치 가능성 및 공공기관 보안 관련 긍정적 전망이 있으나, 일부 하락 의견도 존재.</t>
+          <t>미국 원전주 상승세와 더불어 하반기 상승 전망이 있으나, 수주 발표 이후 주가 하락에 대한 의문과 대차해지 운동 참여 독려가 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '공공기관 보안', '20000원 돌파']</t>
+          <t>['미국 원전주', '하반기 전망', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>260000</v>
+        <v>260500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.97%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G14" t="n">
-        <v>1926</v>
+        <v>1920</v>
       </c>
       <c r="H14" t="n">
         <v>46.48</v>
@@ -1714,7 +1714,7 @@
         <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>2083279902750</v>
+        <v>2150633481750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52400</v>
+        <v>52600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="H15" t="n">
         <v>38.54</v>
@@ -1806,7 +1806,7 @@
         <v>38.62</v>
       </c>
       <c r="O15" t="n">
-        <v>220826005400</v>
+        <v>222970085400</v>
       </c>
       <c r="P15" t="n">
         <v>67300</v>
@@ -1851,70 +1851,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18960</v>
+        <v>17730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>438</v>
+        <v>171</v>
       </c>
       <c r="H16" t="n">
-        <v>10.74</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18490</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>18900</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>19700</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>18760</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
-        <v>10.85</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>121034808855</v>
+        <v>82795995210</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>365000</v>
+        <v>-123000</v>
       </c>
       <c r="S16" t="n">
-        <v>134000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전주 상승세와 더불어 하반기 상승 전망이 있으나, 수주 발표 이후 주가 하락에 대한 의문과 대차해지 운동 참여 독려가 나타남.</t>
+          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['미국 원전주', '하반기 전망', '대차해지']</t>
+          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85600</v>
+        <v>4200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+2.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>1239</v>
+        <v>190</v>
       </c>
       <c r="H17" t="n">
-        <v>23.23</v>
+        <v>0.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85400</v>
+        <v>4095</v>
       </c>
       <c r="K17" t="n">
-        <v>87300</v>
+        <v>4200</v>
       </c>
       <c r="L17" t="n">
-        <v>87800</v>
+        <v>4400</v>
       </c>
       <c r="M17" t="n">
-        <v>85100</v>
+        <v>4095</v>
       </c>
       <c r="N17" t="n">
-        <v>23.27</v>
+        <v>0.87</v>
       </c>
       <c r="O17" t="n">
-        <v>109421491250</v>
+        <v>66830229983</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R17" t="n">
-        <v>-447000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 대미 투자 발표 가능성 뉴스에 따른 기대감 형성. 연기금 매도세는 부담 요인.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '연기금']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13390</v>
+        <v>85500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="G18" t="n">
-        <v>341</v>
+        <v>1256</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L18" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M18" t="n">
-        <v>13280</v>
+        <v>85100</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>40933118220</v>
+        <v>111013266150</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-78000</v>
+        <v>-447000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 진행 여부에 대한 기대와 부정적인 전망이 교차하며, 단기 급등 후 급락 가능성에 대한 우려가 있음.</t>
+          <t>미국 원전주 급등 및 대미 투자 발표 가능성 뉴스에 따른 기대감 형성. 연기금 매도세는 부담 요인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체', '급등락', '기대감']</t>
+          <t>['원전주', '대미 투자', '연기금']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10140</v>
+        <v>13370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.43%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>166</v>
+        <v>357</v>
       </c>
       <c r="H19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,183 +2159,183 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10500</v>
+        <v>13360</v>
       </c>
       <c r="K19" t="n">
-        <v>10650</v>
+        <v>13450</v>
       </c>
       <c r="L19" t="n">
-        <v>10710</v>
+        <v>14450</v>
       </c>
       <c r="M19" t="n">
-        <v>10100</v>
+        <v>13280</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>32860812090</v>
+        <v>41115932650</v>
       </c>
       <c r="P19" t="n">
-        <v>15960</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-117000</v>
+        <v>-78000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17300</v>
+        <v>10120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.51%</t>
+          <t>'-3.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.38</v>
+        <v>-0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>376</v>
+        <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17930</v>
+        <v>10500</v>
       </c>
       <c r="K20" t="n">
-        <v>18400</v>
+        <v>10650</v>
       </c>
       <c r="L20" t="n">
-        <v>20400</v>
+        <v>10710</v>
       </c>
       <c r="M20" t="n">
-        <v>17270</v>
+        <v>10100</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>80015155520</v>
+        <v>33156211570</v>
       </c>
       <c r="P20" t="n">
-        <v>21100</v>
+        <v>15960</v>
       </c>
       <c r="Q20" t="n">
-        <v>9900</v>
+        <v>3500</v>
       </c>
       <c r="R20" t="n">
-        <v>32000</v>
+        <v>-117000</v>
       </c>
       <c r="S20" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>머크사의 3상 임상 진행 소식에도 불구하고 락업 해제 물량 부담 및 주가 하락 가능성에 대한 우려가 있으며, 단기 매매를 권장하는 의견이 다수.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['락업 해제', '머크 3상', '단기 매매']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4210</v>
+        <v>17280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.4</v>
+        <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>224</v>
+        <v>155</v>
       </c>
       <c r="F21" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>829</v>
+        <v>386</v>
       </c>
       <c r="H21" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4635</v>
+        <v>17930</v>
       </c>
       <c r="K21" t="n">
-        <v>4465</v>
+        <v>18400</v>
       </c>
       <c r="L21" t="n">
-        <v>4535</v>
+        <v>20400</v>
       </c>
       <c r="M21" t="n">
-        <v>4125</v>
+        <v>17270</v>
       </c>
       <c r="N21" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="O21" t="n">
-        <v>36649525244</v>
+        <v>81115991150</v>
       </c>
       <c r="P21" t="n">
-        <v>6900</v>
+        <v>21100</v>
       </c>
       <c r="Q21" t="n">
-        <v>1738</v>
+        <v>9900</v>
       </c>
       <c r="R21" t="n">
-        <v>-93000</v>
+        <v>32000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 코인 관련 호재 언급. 주포 물량 넘김 및 탈출 경고.</t>
+          <t>단기 트레이딩에 적합한 종목으로 평가되며, 락업 해제 물량 소화 및 주포의 움직임에 대한 분석이 존재함. 바이오 섹터의 대세장 가능성이 언급되나, 목표 주가에 대한 기대와 현재 주가의 괴리에 대한 의견이 교차함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['STO', '코인']</t>
+          <t>['락업해제', '주포', '바이오']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>4190</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-46.51%</t>
+          <t>'-9.60%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.02</v>
+        <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="G22" t="n">
-        <v>133</v>
+        <v>833</v>
       </c>
       <c r="H22" t="n">
-        <v>3.69</v>
+        <v>0.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,58 +2435,150 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>43</v>
+        <v>4635</v>
       </c>
       <c r="K22" t="n">
-        <v>44</v>
+        <v>4465</v>
       </c>
       <c r="L22" t="n">
-        <v>44</v>
+        <v>4535</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>4125</v>
       </c>
       <c r="N22" t="n">
-        <v>3.71</v>
+        <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>173053965</v>
+        <v>36955598464</v>
       </c>
       <c r="P22" t="n">
-        <v>901</v>
+        <v>6900</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>1738</v>
       </c>
       <c r="R22" t="n">
-        <v>-58000</v>
+        <v>-93000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>장외 거래 및 대주주 변경 가능성에 대한 기대감과 함께, 현재 주가에 대한 부정적인 의견 및 개미 투자자들의 행태에 대한 비판이 공존.</t>
+          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['STO', '코인 테마', '주포 물량']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-46.51%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>99</v>
+      </c>
+      <c r="F23" t="n">
+        <v>38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>136</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>43</v>
+      </c>
+      <c r="K23" t="n">
+        <v>44</v>
+      </c>
+      <c r="L23" t="n">
+        <v>44</v>
+      </c>
+      <c r="M23" t="n">
+        <v>23</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O23" t="n">
+        <v>173053965</v>
+      </c>
+      <c r="P23" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>23</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>K-OTC 시장 거래 및 대주주 전환 기대감에도 불구하고, 투자자들의 매수세 부진과 급격한 가격 하락이 관찰됨. 일부 투자자들은 추가 매수를 준비하나, 전반적으로 회의적인 시각이 존재함.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>0.1</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>['장외 거래', '대주주 변경', '현재 주가']</t>
-        </is>
-      </c>
-      <c r="X22" t="n">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['K-OTC', '대주주', '장외거래']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>2</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>008290</t>
         </is>
